--- a/results/Int Task Remove ACC 0.3/Rando_7_permute.xlsx
+++ b/results/Int Task Remove ACC 0.3/Rando_7_permute.xlsx
@@ -440,7 +440,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6558745446089451</v>
+        <v>0.6862274888251556</v>
       </c>
     </row>
     <row r="3">
@@ -450,317 +450,317 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6552124512311708</v>
+        <v>0.6811971940159678</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6721297444642534</v>
+        <v>0.6852876392010956</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6771245123117071</v>
+        <v>0.6834612303955766</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6749315298555667</v>
+        <v>0.6835678112807793</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6738205048704236</v>
+        <v>0.6835678112807793</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6738205048704236</v>
+        <v>0.688715991008449</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6706876727902229</v>
+        <v>0.6877583779035217</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6799440611838876</v>
+        <v>0.6877583779035217</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6743404904012609</v>
+        <v>0.6880716611115418</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.673749450946955</v>
+        <v>0.6890825646590704</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6888338759269308</v>
+        <v>0.6838988579696664</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6888338759269308</v>
+        <v>0.6868605146887838</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6873207503294319</v>
+        <v>0.6843364855437563</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6857543342893315</v>
+        <v>0.679093028964163</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6613650750587809</v>
+        <v>0.6969033408262926</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.661991641474821</v>
+        <v>0.6972166240343126</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6559504431181046</v>
+        <v>0.6981742371392399</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6707700307469706</v>
+        <v>0.6949348241738367</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6739561532697724</v>
+        <v>0.7105456941322378</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6752448130635869</v>
+        <v>0.71392075549699</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6731761749735163</v>
+        <v>0.7151383613673359</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6699367620081131</v>
+        <v>0.7113079089476269</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6374554298116425</v>
+        <v>0.7132344391907603</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6359067772524094</v>
+        <v>0.7132344391907603</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6163104281321862</v>
+        <v>0.7091084670438984</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6105292225408883</v>
+        <v>0.7084641371469912</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6096248998785624</v>
+        <v>0.7052424876624551</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6060011497816706</v>
+        <v>0.7000587809730512</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6339075782239103</v>
+        <v>0.6992965661576622</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6438260599953493</v>
+        <v>0.7092861018525696</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6540174534273828</v>
+        <v>0.7130455003488101</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.6579900136940289</v>
+        <v>0.7069687750303594</v>
       </c>
     </row>
     <row r="35">
@@ -770,277 +770,277 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.6573456837971217</v>
+        <v>0.7056801152365449</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6573456837971217</v>
+        <v>0.6087803271064258</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6493182053070821</v>
+        <v>0.6054763196651423</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6276709815776556</v>
+        <v>0.6061028860811823</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6515176472108105</v>
+        <v>0.5874060150375939</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6488757331473012</v>
+        <v>0.5954690204893678</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6402152287936336</v>
+        <v>0.5775698912229026</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6515160323489135</v>
+        <v>0.5775698912229026</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.6623630597111335</v>
+        <v>0.5688157248792083</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.665200372064181</v>
+        <v>0.5665694519804666</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.658763532542697</v>
+        <v>0.5634899103428674</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.6963397540242359</v>
+        <v>0.5634899103428674</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.642571312301372</v>
+        <v>0.5342124641500658</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.608953117329406</v>
+        <v>0.5282294008216417</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.6276919747823166</v>
+        <v>0.4959789938764437</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.6104371754127587</v>
+        <v>0.4283501924915382</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5810579929204455</v>
+        <v>0.4203275585871896</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5784629098519495</v>
+        <v>0.43399413482159</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.6333036198744284</v>
+        <v>0.434289654548743</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.6173843112936982</v>
+        <v>0.4429550034881017</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5726833191225487</v>
+        <v>0.4511714208200915</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5867746040358629</v>
+        <v>0.444681290856006</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5434559336485544</v>
+        <v>0.4402646435676821</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5077400330723717</v>
+        <v>0.4584883600754464</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5074445133452187</v>
+        <v>0.4762631449758417</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5194380926543162</v>
+        <v>0.4716704777407436</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5076286076014779</v>
+        <v>0.504889801824148</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5317691780998889</v>
+        <v>0.494189726894556</v>
       </c>
     </row>
     <row r="63">
@@ -1050,277 +1050,277 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5216908250006459</v>
+        <v>0.4956673255303206</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5216908250006459</v>
+        <v>0.4994977779500297</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.512839766943131</v>
+        <v>0.4994977779500297</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5264062217399168</v>
+        <v>0.5000532904426014</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5172967857788802</v>
+        <v>0.4997400072345813</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5247509882954809</v>
+        <v>0.4997400072345813</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5337716068521819</v>
+        <v>0.4997222437537142</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5337716068521819</v>
+        <v>0.4997044802728471</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.4988001576105212</v>
+        <v>0.4997044802728471</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.499846588119784</v>
+        <v>0.4997044802728471</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5038191483864299</v>
+        <v>0.4990601503759399</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5096003539777278</v>
+        <v>0.49968671679198</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.4956447174637625</v>
+        <v>0.49968671679198</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.4879660491434772</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.4808735756918068</v>
+        <v>0.49968671679198</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.4698795958969589</v>
+        <v>0.4974937343358396</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.4698795958969589</v>
+        <v>0.4990779138568069</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.4698795958969589</v>
+        <v>0.4984513474407669</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.4814355476319666</v>
+        <v>0.4998643516006511</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5283537451877116</v>
+        <v>0.4960871896235434</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5201421724414128</v>
+        <v>0.495407332764902</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5141235821512544</v>
+        <v>0.5013597137172829</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.4999596284525747</v>
+        <v>0.5049479368524403</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.4882728729039092</v>
+        <v>0.5049479368524403</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4839224349533627</v>
+        <v>0.5049479368524403</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.4796608144071519</v>
+        <v>0.5052967470221946</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.4794185851226003</v>
+        <v>0.5013597137172829</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5004085600599436</v>
+        <v>0.5024239077074129</v>
       </c>
     </row>
   </sheetData>
